--- a/X-Series/XD12R/Jig/XCR_XDR/XC24RV_XD12RV/Docs/GT/XCR_TEST_PLAN_260706.xlsx
+++ b/X-Series/XD12R/Jig/XCR_XDR/XC24RV_XD12RV/Docs/GT/XCR_TEST_PLAN_260706.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sosbi\OneDrive\바탕 화면\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\working\01_Project\FW\X-Series\XD12R\Jig\XCR_XDR\XC24RV_XD12RV\Docs\GT\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{12791A1A-242A-42D3-800D-85B54DABEF80}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="40160" yWindow="1160" windowWidth="35320" windowHeight="18180" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="71880" yWindow="2160" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Test_Plan" sheetId="2" r:id="rId1"/>
